--- a/uat-test-plans-reduced30/G2-16176-site-header-set-up.xlsx
+++ b/uat-test-plans-reduced30/G2-16176-site-header-set-up.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced ~30% — 7/10 checks retained, lowest-priority sections dropped] 11 UI-testable stories/bugs mapped to 10 business checklist checks and 11 coverage rows. 2 QA execution tasks excluded as non-product-capability items.</t>
+          <t>[Reduced V2 ~20% — 8/10 checks retained; AC and core-case coverage guardrails enforced] 11 UI-testable stories/bugs mapped to 10 business checklist checks and 11 coverage rows. 2 QA execution tasks excluded as non-product-capability items.</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=10583; payload_chars=10579; est_tokens~2645; checklist_rows=7; matrix_rows=8; exploratory_rows=3</t>
+          <t>payload_bytes=12196; payload_chars=12192; est_tokens~3048; checklist_rows=8; matrix_rows=11; exploratory_rows=3</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -907,10 +907,10 @@
       <c r="G5" s="5" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr"/>
     </row>
-    <row r="6" ht="49" customHeight="1">
+    <row r="6" ht="64" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>UAT-005</t>
+          <t>UAT-007</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -920,32 +920,33 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Search &amp; Meganav</t>
+          <t>Scroll Behavior</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Search entry point and meganav host placeholder are present</t>
+          <t>PDP desktop no longer shows sticky header on up-scroll</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>On NAP and MRP, verify search icon/entry point is available and the header area reserves space for meganav hosting behavior.</t>
+          <t>1. Open a PDP on desktop and scroll down then up.
+2. Confirm the sticky header does not reappear and obscure product content.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Search entry point is visible and actionable.
-Meganav host area is present without layout breakage.</t>
+          <t>Header does not become sticky on PDP up-scroll for desktop.
+PDP content remains unobstructed during scroll interactions.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
     </row>
-    <row r="7" ht="79" customHeight="1">
+    <row r="7" ht="64" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>UAT-006</t>
+          <t>UAT-008</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -955,24 +956,23 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Responsive Behavior</t>
+          <t>Auth Transition Animation</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Header works across desktop and mobile web including hamburger menu</t>
+          <t>Header animation is stable during logout/login transitions</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>1. Test NAP and MRP on desktop and mobile breakpoints.
-2. Validate hamburger behavior on mobile and core header action availability at each breakpoint.</t>
+          <t>Perform login and logout flows on NAP/MRP and observe header brand/name animation behavior during transition moments.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Core header actions remain accessible on all tested breakpoints.
-Mobile hamburger navigation appears and functions as expected.</t>
+          <t>No header flicker or broken animation appears during auth transitions.
+Logo/name animation remains smooth and readable.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
@@ -981,7 +981,7 @@
     <row r="8" ht="64" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>UAT-007</t>
+          <t>UAT-009</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -991,28 +991,62 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Scroll Behavior</t>
+          <t>Name Clipping (Mobile)</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>PDP desktop no longer shows sticky header on up-scroll</t>
+          <t>Customer name is not clipped in mobile header animation</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>1. Open a PDP on desktop and scroll down then up.
-2. Confirm the sticky header does not reappear and obscure product content.</t>
+          <t>On iOS Safari mobile (or simulator), log in and observe header animation where customer name appears.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Header does not become sticky on PDP up-scroll for desktop.
-PDP content remains unobstructed during scroll interactions.</t>
+          <t>Customer name text remains fully visible during animation.
+No vertical clipping is visible in the header greeting area.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="64" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>UAT-010</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Sane, Sridevi Mayuresh || LuxExperience</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Name Clipping (Desktop)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Customer name is not clipped on Windows desktop browsers</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>On Windows Chrome, log in to NAP/MRP and observe the rolling customer name in header.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Customer name is fully visible in header greeting area.
+No clipping occurs at top or bottom of text line.</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1025,7 +1059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1033,7 +1067,7 @@
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
@@ -1285,7 +1319,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>UAT-001, UAT-005, UAT-006</t>
+          <t>UAT-001</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1525,6 +1559,169 @@
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>COV-009</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>G2-22132</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Bugfix-Logout-Animation</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Logout header animation stability</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>UAT-008</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>PRs #525 and #526 [G2-22132] in mytheresa/atelier.</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>COV-010</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>G2-22476</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Bugfix-Mobile-Name-Clip</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Customer name rendering without clipping on mobile</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>UAT-009</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>PR #602 [G2-22476] in mytheresa/atelier.</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="49" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>COV-011</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>G2-22702</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Bugfix-Desktop-Name-Clip</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Customer name rendering without clipping on Windows desktop</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>UAT-010</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>No direct PR hit for G2-22702; related Jira link points to G2-22708 with PR #824.</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Evidence is indirect via linked bug ticket; direct implementation linkage should be confirmed in Jira history.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/uat-test-plans-reduced30/G2-16176-site-header-set-up.xlsx
+++ b/uat-test-plans-reduced30/G2-16176-site-header-set-up.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced V2 ~20% — 8/10 checks retained; AC and core-case coverage guardrails enforced] 11 UI-testable stories/bugs mapped to 10 business checklist checks and 11 coverage rows. 2 QA execution tasks excluded as non-product-capability items.</t>
+          <t>[Reduced V2 ~20% — 8/10 checks retained; AC coverage guardrail enforced] 11 UI-testable stories/bugs mapped to 10 business checklist checks and 11 coverage rows. 2 QA execution tasks excluded as non-product-capability items.</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=12196; payload_chars=12192; est_tokens~3048; checklist_rows=8; matrix_rows=11; exploratory_rows=3</t>
+          <t>payload_bytes=12181; payload_chars=12177; est_tokens~3045; checklist_rows=8; matrix_rows=11; exploratory_rows=3</t>
         </is>
       </c>
     </row>
